--- a/dados/importados/Pneuport.xlsx
+++ b/dados/importados/Pneuport.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EsteLivro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\servidor\Utilizadores\Pedro Morgado\PedroPC\Ambiente Trabalho\Lis_camp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pedro Morgado\Desktop\Dashboard\Geral\DMClientes\DMClientes\dados\importados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6526B260-4CF1-4601-B251-AED34D32B57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8328ECDD-868F-4F0E-BCBA-E8D8BBECCC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C02A5042-19D9-464B-96CB-3EAF8D0BD027}"/>
   </bookViews>
@@ -18,23 +18,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Registos!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="353">
   <si>
     <t>COOP.</t>
   </si>
@@ -1121,6 +1110,30 @@
   </si>
   <si>
     <t>Pneuport</t>
+  </si>
+  <si>
+    <t>Distrito</t>
+  </si>
+  <si>
+    <t>LISBOA</t>
+  </si>
+  <si>
+    <t>SETÚBAL</t>
+  </si>
+  <si>
+    <t>BRAGANÇA</t>
+  </si>
+  <si>
+    <t>BRAGA</t>
+  </si>
+  <si>
+    <t>FARO</t>
+  </si>
+  <si>
+    <t>SANTAREM</t>
+  </si>
+  <si>
+    <t>PORTO</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1483,9 +1496,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1501,7 +1511,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1510,24 +1520,15 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1543,7 +1544,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1552,12 +1553,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1579,10 +1574,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1603,7 +1595,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1612,9 +1604,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1630,18 +1619,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1651,7 +1634,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1659,9 +1642,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1690,7 +1670,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>9551</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1780,7 +1760,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>620971</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1870,7 +1850,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>620971</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2303,7 +2283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A228DCB-E925-4448-878C-5B14C9016780}">
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -2311,18 +2291,18 @@
     <col min="3" max="3" width="4.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="48.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="46.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="24.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="31.42578125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="7" width="22.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="24.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="31.42578125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" ht="13.5" thickBot="1">
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="13.5" thickBot="1">
       <c r="A1" s="7" t="s">
         <v>338</v>
       </c>
@@ -2341,23 +2321,26 @@
       <c r="F1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="2" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B2" s="12" t="s">
         <v>344</v>
       </c>
@@ -2373,1843 +2356,1953 @@
       <c r="F2" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="H2" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="H2" s="18">
+      <c r="I2" s="18">
         <v>213538695</v>
       </c>
-      <c r="I2" s="19">
+      <c r="J2" s="19">
         <v>213575019</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="K2" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="L2" s="16" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="12" customFormat="1" ht="31.5">
+    <row r="3" spans="1:12" s="12" customFormat="1" ht="31.5">
       <c r="B3" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="21">
         <v>3</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="H3" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="27">
+      <c r="I3" s="26">
         <v>218436090</v>
       </c>
-      <c r="I3" s="28">
+      <c r="J3" s="27">
         <v>218475315</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="K3" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="L3" s="29" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="4" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B4" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="21">
         <v>10</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="24"/>
+      <c r="H4" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="27">
+      <c r="I4" s="26">
         <v>212254064</v>
       </c>
-      <c r="I4" s="28">
+      <c r="J4" s="27">
         <v>212246002</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="K4" s="31" t="s">
+      <c r="L4" s="24" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="5" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B5" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="21">
         <v>12</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="30"/>
+      <c r="H5" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="27">
+      <c r="I5" s="26">
         <v>214561327</v>
       </c>
-      <c r="I5" s="28">
+      <c r="J5" s="27">
         <v>214581564</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="K5" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="L5" s="24" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="6" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B6" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="21">
         <v>18</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="H6" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="27">
+      <c r="I6" s="26">
         <v>218121220</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="J6" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="K6" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="K6" s="31" t="s">
+      <c r="L6" s="24" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="7" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B7" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="21">
         <v>23</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="24"/>
+      <c r="H7" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="I7" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="I7" s="28">
+      <c r="J7" s="27">
         <v>212500382</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="K7" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="K7" s="31" t="s">
+      <c r="L7" s="24" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="8" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B8" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="21">
         <v>24</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="24"/>
+      <c r="H8" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="27">
+      <c r="I8" s="26">
         <v>214418248</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="J8" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="J8" s="29" t="s">
+      <c r="K8" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="K8" s="31" t="s">
+      <c r="L8" s="24" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="9" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B9" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="21">
         <v>29</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="24"/>
+      <c r="H9" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="I9" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="I9" s="28">
+      <c r="J9" s="27">
         <v>261816009</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="K9" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="K9" s="31" t="s">
+      <c r="L9" s="24" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="10" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B10" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="21">
         <v>33</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="24"/>
+      <c r="H10" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="35">
+      <c r="I10" s="26">
         <v>212157654</v>
       </c>
-      <c r="I10" s="33" t="s">
+      <c r="J10" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="K10" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="K10" s="31" t="s">
+      <c r="L10" s="24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="11" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B11" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="21">
         <v>35</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="H11" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="27">
+      <c r="I11" s="26">
         <v>218681256</v>
       </c>
-      <c r="I11" s="28">
+      <c r="J11" s="27">
         <v>218684162</v>
       </c>
-      <c r="J11" s="29" t="s">
+      <c r="K11" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="K11" s="31" t="s">
+      <c r="L11" s="24" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="12" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B12" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="21">
         <v>38</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="H12" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="H12" s="27">
+      <c r="I12" s="26">
         <v>265533343</v>
       </c>
-      <c r="I12" s="33" t="s">
+      <c r="J12" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="29" t="s">
+      <c r="K12" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="K12" s="31" t="s">
+      <c r="L12" s="24" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="13" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B13" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="21">
         <v>47</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="24" t="s">
         <v>260</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="24"/>
+      <c r="H13" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="27">
+      <c r="I13" s="26">
         <v>249760241</v>
       </c>
-      <c r="I13" s="28">
+      <c r="J13" s="27">
         <v>249760241</v>
       </c>
-      <c r="J13" s="29" t="s">
+      <c r="K13" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="K13" s="31" t="s">
+      <c r="L13" s="24" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="14" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B14" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <v>55</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="H14" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="27">
+      <c r="I14" s="26">
         <v>281512779</v>
       </c>
-      <c r="I14" s="28">
+      <c r="J14" s="27">
         <v>281541231</v>
       </c>
-      <c r="J14" s="29" t="s">
+      <c r="K14" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="K14" s="31" t="s">
+      <c r="L14" s="24" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="15" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B15" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="21">
         <v>56</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="24"/>
+      <c r="H15" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H15" s="30" t="s">
+      <c r="I15" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="I15" s="28">
+      <c r="J15" s="27">
         <v>219270700</v>
       </c>
-      <c r="J15" s="29" t="s">
+      <c r="K15" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="K15" s="31" t="s">
+      <c r="L15" s="24" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="16" spans="1:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B16" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="21">
         <v>58</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="H16" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="H16" s="35">
+      <c r="I16" s="26">
         <v>218146262</v>
       </c>
-      <c r="I16" s="28">
+      <c r="J16" s="27">
         <v>218127699</v>
       </c>
-      <c r="J16" s="29" t="s">
+      <c r="K16" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="K16" s="31" t="s">
+      <c r="L16" s="24" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="17" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B17" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="21">
         <v>62</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="G17" s="24"/>
+      <c r="H17" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="35">
+      <c r="I17" s="26">
         <v>214358851</v>
       </c>
-      <c r="I17" s="28">
+      <c r="J17" s="27">
         <v>214358951</v>
       </c>
-      <c r="J17" s="29" t="s">
+      <c r="K17" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="K17" s="31" t="s">
+      <c r="L17" s="24" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="18" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B18" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="21">
         <v>63</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="G18" s="26" t="s">
+      <c r="G18" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="H18" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="35" t="s">
+      <c r="I18" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="I18" s="28">
+      <c r="J18" s="27">
         <v>217962556</v>
       </c>
-      <c r="J18" s="29" t="s">
+      <c r="K18" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="K18" s="31" t="s">
+      <c r="L18" s="24" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="19" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B19" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="21">
         <v>68</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="F19" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="24"/>
+      <c r="H19" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="H19" s="35">
+      <c r="I19" s="26">
         <v>219806930</v>
       </c>
-      <c r="I19" s="28">
+      <c r="J19" s="27">
         <v>219800196</v>
       </c>
-      <c r="J19" s="29" t="s">
+      <c r="K19" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="K19" s="31" t="s">
+      <c r="L19" s="24" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="20" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B20" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="21">
         <v>70</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F20" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="24"/>
+      <c r="H20" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="H20" s="35">
+      <c r="I20" s="26">
         <v>244840419</v>
       </c>
-      <c r="I20" s="28">
+      <c r="J20" s="27">
         <v>244841221</v>
       </c>
-      <c r="J20" s="29" t="s">
+      <c r="K20" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="K20" s="31" t="s">
+      <c r="L20" s="24" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="21" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B21" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="21">
         <v>72</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="G21" s="24"/>
+      <c r="H21" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="H21" s="35">
+      <c r="I21" s="26">
         <v>261461180</v>
       </c>
-      <c r="I21" s="28">
+      <c r="J21" s="27">
         <v>261461180</v>
       </c>
-      <c r="J21" s="29" t="s">
+      <c r="K21" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="K21" s="31" t="s">
+      <c r="L21" s="24" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="22" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B22" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="21">
         <v>75</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G22" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="H22" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="H22" s="35">
+      <c r="I22" s="26">
         <v>289414688</v>
       </c>
-      <c r="I22" s="28">
+      <c r="J22" s="27">
         <v>289414688</v>
       </c>
-      <c r="J22" s="29" t="s">
+      <c r="K22" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="K22" s="31" t="s">
+      <c r="L22" s="24" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="23" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B23" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="21">
         <v>77</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="24"/>
+      <c r="H23" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="H23" s="35">
+      <c r="I23" s="26">
         <v>212223837</v>
       </c>
-      <c r="I23" s="28" t="s">
+      <c r="J23" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="J23" s="29" t="s">
+      <c r="K23" s="28" t="s">
         <v>233</v>
       </c>
-      <c r="K23" s="31" t="s">
+      <c r="L23" s="24" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="24" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B24" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="21">
         <v>79</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="24"/>
+      <c r="H24" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="I24" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="I24" s="28">
+      <c r="J24" s="27">
         <v>212744457</v>
       </c>
-      <c r="J24" s="29" t="s">
+      <c r="K24" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="K24" s="31" t="s">
+      <c r="L24" s="24" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="25" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B25" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="21">
         <v>82</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="F25" s="25" t="s">
+      <c r="F25" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G25" s="24"/>
+      <c r="H25" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="H25" s="35">
+      <c r="I25" s="26">
         <v>295542072</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="J25" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="J25" s="29" t="s">
+      <c r="K25" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="K25" s="31" t="s">
+      <c r="L25" s="24" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="26" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B26" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="21">
         <v>89</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="F26" s="25" t="s">
+      <c r="F26" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="26" t="s">
+      <c r="G26" s="24"/>
+      <c r="H26" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="H26" s="35">
+      <c r="I26" s="26">
         <v>243405552</v>
       </c>
-      <c r="I26" s="28">
+      <c r="J26" s="27">
         <v>243405552</v>
       </c>
-      <c r="J26" s="29" t="s">
+      <c r="K26" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="K26" s="31" t="s">
+      <c r="L26" s="24" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="27" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B27" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="21">
         <v>90</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="25" t="s">
+      <c r="F27" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="24"/>
+      <c r="H27" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="H27" s="35" t="s">
+      <c r="I27" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="I27" s="28">
+      <c r="J27" s="27">
         <v>234648143</v>
       </c>
-      <c r="J27" s="29" t="s">
+      <c r="K27" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="K27" s="31" t="s">
+      <c r="L27" s="24" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="28" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B28" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="21">
         <v>94</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="F28" s="25" t="s">
+      <c r="F28" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="G28" s="26" t="s">
+      <c r="G28" s="24"/>
+      <c r="H28" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="H28" s="35">
+      <c r="I28" s="26">
         <v>255432099</v>
       </c>
-      <c r="I28" s="28" t="s">
+      <c r="J28" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="J28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="K28" s="31" t="s">
+      <c r="L28" s="24" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="29" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B29" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="21">
         <v>95</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F29" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="G29" s="26" t="s">
+      <c r="G29" s="24"/>
+      <c r="H29" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="H29" s="25" t="s">
+      <c r="I29" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I29" s="28">
+      <c r="J29" s="27">
         <v>255539188</v>
       </c>
-      <c r="J29" s="29" t="s">
+      <c r="K29" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="K29" s="31" t="s">
+      <c r="L29" s="24" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="30" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B30" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="21">
         <v>100</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="F30" s="25" t="s">
+      <c r="F30" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="24"/>
+      <c r="H30" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="H30" s="27">
+      <c r="I30" s="26">
         <v>261857279</v>
       </c>
-      <c r="I30" s="28">
+      <c r="J30" s="27">
         <v>261858458</v>
       </c>
-      <c r="J30" s="29" t="s">
+      <c r="K30" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="K30" s="31" t="s">
+      <c r="L30" s="24" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="31" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B31" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="21">
         <v>101</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="F31" s="25" t="s">
+      <c r="F31" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="G31" s="26" t="s">
+      <c r="G31" s="24"/>
+      <c r="H31" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="H31" s="27">
+      <c r="I31" s="26">
         <v>214991982</v>
       </c>
-      <c r="I31" s="28">
+      <c r="J31" s="27">
         <v>214998442</v>
       </c>
-      <c r="J31" s="29" t="s">
+      <c r="K31" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="K31" s="31" t="s">
+      <c r="L31" s="24" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="32" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B32" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="21">
         <v>102</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="F32" s="25" t="s">
+      <c r="F32" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="24"/>
+      <c r="H32" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="H32" s="27">
+      <c r="I32" s="26">
         <v>261961134</v>
       </c>
-      <c r="I32" s="28">
+      <c r="J32" s="27">
         <v>261961102</v>
       </c>
-      <c r="J32" s="29" t="s">
+      <c r="K32" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="K32" s="31" t="s">
+      <c r="L32" s="24" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="33" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B33" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="21">
         <v>109</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="F33" s="25" t="s">
+      <c r="F33" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="G33" s="26" t="s">
+      <c r="G33" s="24"/>
+      <c r="H33" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="H33" s="27">
+      <c r="I33" s="26">
         <v>281511694</v>
       </c>
-      <c r="I33" s="28" t="s">
+      <c r="J33" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="J33" s="29" t="s">
+      <c r="K33" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="K33" s="31" t="s">
+      <c r="L33" s="24" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="34" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B34" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="32">
         <v>110</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="D34" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="E34" s="38" t="s">
+      <c r="E34" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="F34" s="39" t="s">
+      <c r="F34" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="G34" s="40" t="s">
+      <c r="G34" s="35" t="s">
+        <v>351</v>
+      </c>
+      <c r="H34" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="H34" s="41">
+      <c r="I34" s="37">
         <v>219608100</v>
       </c>
-      <c r="I34" s="42" t="s">
+      <c r="J34" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="J34" s="43" t="s">
+      <c r="K34" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="K34" s="44" t="s">
+      <c r="L34" s="35" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="35" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="35" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B35" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="32">
         <v>111</v>
       </c>
-      <c r="D35" s="38" t="s">
+      <c r="D35" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="E35" s="38" t="s">
+      <c r="E35" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="F35" s="39" t="s">
+      <c r="F35" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="G35" s="40" t="s">
+      <c r="G35" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="H35" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="H35" s="41">
+      <c r="I35" s="37">
         <v>252607830</v>
       </c>
-      <c r="I35" s="42" t="s">
+      <c r="J35" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="J35" s="29" t="s">
+      <c r="K35" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="K35" s="44" t="s">
+      <c r="L35" s="35" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="36" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="36" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B36" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="32">
         <v>112</v>
       </c>
-      <c r="D36" s="38" t="s">
+      <c r="D36" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="E36" s="38" t="s">
+      <c r="E36" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="F36" s="39" t="s">
+      <c r="F36" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="G36" s="40" t="s">
+      <c r="G36" s="35"/>
+      <c r="H36" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H36" s="41">
+      <c r="I36" s="37">
         <v>253584941</v>
       </c>
-      <c r="I36" s="42" t="s">
+      <c r="J36" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="J36" s="29" t="s">
+      <c r="K36" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K36" s="44" t="s">
+      <c r="L36" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="37" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B37" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C37" s="36">
+      <c r="C37" s="32">
         <v>112</v>
       </c>
-      <c r="D37" s="38" t="s">
+      <c r="D37" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="38" t="s">
+      <c r="E37" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="F37" s="39" t="s">
+      <c r="F37" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="G37" s="40" t="s">
+      <c r="G37" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="H37" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H37" s="41">
+      <c r="I37" s="37">
         <v>229510434</v>
       </c>
-      <c r="I37" s="42"/>
-      <c r="J37" s="29" t="s">
+      <c r="J37" s="38"/>
+      <c r="K37" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K37" s="44" t="s">
+      <c r="L37" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="38" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="38" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B38" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="32">
         <v>112</v>
       </c>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="E38" s="38" t="s">
+      <c r="E38" s="34" t="s">
         <v>333</v>
       </c>
-      <c r="F38" s="39" t="s">
+      <c r="F38" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="G38" s="40" t="s">
+      <c r="G38" s="35" t="s">
+        <v>349</v>
+      </c>
+      <c r="H38" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H38" s="41">
+      <c r="I38" s="37">
         <v>252857026</v>
       </c>
-      <c r="I38" s="42"/>
-      <c r="J38" s="29" t="s">
+      <c r="J38" s="38"/>
+      <c r="K38" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K38" s="44" t="s">
+      <c r="L38" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="39" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="39" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B39" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="32">
         <v>112</v>
       </c>
-      <c r="D39" s="38" t="s">
+      <c r="D39" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="E39" s="38" t="s">
+      <c r="E39" s="34" t="s">
         <v>331</v>
       </c>
-      <c r="F39" s="39" t="s">
+      <c r="F39" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G39" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="H39" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H39" s="41">
+      <c r="I39" s="37">
         <v>227821146</v>
       </c>
-      <c r="I39" s="45"/>
-      <c r="J39" s="29" t="s">
+      <c r="J39" s="36"/>
+      <c r="K39" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K39" s="44" t="s">
+      <c r="L39" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="40" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B40" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="32">
         <v>112</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="E40" s="38" t="s">
+      <c r="E40" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="F40" s="39" t="s">
+      <c r="F40" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="G40" s="40" t="s">
+      <c r="G40" s="35"/>
+      <c r="H40" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H40" s="41">
+      <c r="I40" s="37">
         <v>278262149</v>
       </c>
-      <c r="I40" s="42"/>
-      <c r="J40" s="29" t="s">
+      <c r="J40" s="38"/>
+      <c r="K40" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K40" s="44" t="s">
+      <c r="L40" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="41" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="41" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B41" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="32">
         <v>112</v>
       </c>
-      <c r="D41" s="38" t="s">
+      <c r="D41" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="E41" s="38" t="s">
+      <c r="E41" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="F41" s="39" t="s">
+      <c r="F41" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="G41" s="40" t="s">
+      <c r="G41" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="H41" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H41" s="41">
+      <c r="I41" s="37">
         <v>223204079</v>
       </c>
-      <c r="I41" s="42"/>
-      <c r="J41" s="29" t="s">
+      <c r="J41" s="38"/>
+      <c r="K41" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K41" s="44" t="s">
+      <c r="L41" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="42" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B42" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C42" s="36">
+      <c r="C42" s="32">
         <v>112</v>
       </c>
-      <c r="D42" s="38" t="s">
+      <c r="D42" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="E42" s="38" t="s">
+      <c r="E42" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="F42" s="39" t="s">
+      <c r="F42" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="G42" s="40" t="s">
+      <c r="G42" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="H42" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H42" s="41">
+      <c r="I42" s="37">
         <v>252616569</v>
       </c>
-      <c r="I42" s="42"/>
-      <c r="J42" s="29" t="s">
+      <c r="J42" s="38"/>
+      <c r="K42" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K42" s="44" t="s">
+      <c r="L42" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="43" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B43" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C43" s="46">
+      <c r="C43" s="40">
         <v>112</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="E43" s="38" t="s">
+      <c r="E43" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="F43" s="39" t="s">
+      <c r="F43" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="G43" s="40" t="s">
+      <c r="G43" s="35"/>
+      <c r="H43" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H43" s="41">
+      <c r="I43" s="37">
         <v>255926824</v>
       </c>
-      <c r="I43" s="42"/>
-      <c r="J43" s="29" t="s">
+      <c r="J43" s="38"/>
+      <c r="K43" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K43" s="44" t="s">
+      <c r="L43" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="44" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="44" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B44" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="32">
         <v>112</v>
       </c>
-      <c r="D44" s="38" t="s">
+      <c r="D44" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="E44" s="38" t="s">
+      <c r="E44" s="34" t="s">
         <v>325</v>
       </c>
-      <c r="F44" s="39" t="s">
+      <c r="F44" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="G44" s="40" t="s">
+      <c r="G44" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="H44" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H44" s="41">
+      <c r="I44" s="37">
         <v>252850046</v>
       </c>
-      <c r="I44" s="42"/>
-      <c r="J44" s="29" t="s">
+      <c r="J44" s="38"/>
+      <c r="K44" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K44" s="44" t="s">
+      <c r="L44" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="45" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="45" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B45" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="32">
         <v>112</v>
       </c>
-      <c r="D45" s="38" t="s">
+      <c r="D45" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="E45" s="38" t="s">
+      <c r="E45" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="F45" s="39" t="s">
+      <c r="F45" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="G45" s="40" t="s">
+      <c r="G45" s="35"/>
+      <c r="H45" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H45" s="41">
+      <c r="I45" s="37">
         <v>255893146</v>
       </c>
-      <c r="I45" s="42"/>
-      <c r="J45" s="29" t="s">
+      <c r="J45" s="38"/>
+      <c r="K45" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K45" s="44" t="s">
+      <c r="L45" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="46" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B46" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C46" s="36">
+      <c r="C46" s="32">
         <v>112</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="E46" s="38" t="s">
+      <c r="E46" s="34" t="s">
         <v>329</v>
       </c>
-      <c r="F46" s="39" t="s">
+      <c r="F46" s="35" t="s">
         <v>323</v>
       </c>
-      <c r="G46" s="40" t="s">
+      <c r="G46" s="35"/>
+      <c r="H46" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H46" s="41">
+      <c r="I46" s="37">
         <v>255721196</v>
       </c>
-      <c r="I46" s="42"/>
-      <c r="J46" s="29" t="s">
+      <c r="J46" s="38"/>
+      <c r="K46" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K46" s="44" t="s">
+      <c r="L46" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="47" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B47" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="32">
         <v>112</v>
       </c>
-      <c r="D47" s="38" t="s">
+      <c r="D47" s="34" t="s">
         <v>319</v>
       </c>
-      <c r="E47" s="38" t="s">
+      <c r="E47" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="F47" s="39" t="s">
+      <c r="F47" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="G47" s="40" t="s">
+      <c r="G47" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="H47" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="H47" s="41">
+      <c r="I47" s="37">
         <v>229543081</v>
       </c>
-      <c r="I47" s="42"/>
-      <c r="J47" s="29" t="s">
+      <c r="J47" s="38"/>
+      <c r="K47" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="K47" s="44" t="s">
+      <c r="L47" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="48" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="48" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B48" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C48" s="36">
+      <c r="C48" s="32">
         <v>114</v>
       </c>
-      <c r="D48" s="38" t="s">
+      <c r="D48" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="E48" s="38" t="s">
+      <c r="E48" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="F48" s="39" t="s">
+      <c r="F48" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="G48" s="40" t="s">
+      <c r="G48" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="H48" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="H48" s="41">
+      <c r="I48" s="37">
         <v>213528576</v>
       </c>
-      <c r="I48" s="42" t="s">
+      <c r="J48" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="J48" s="43" t="s">
+      <c r="K48" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="K48" s="44" t="s">
+      <c r="L48" s="35" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="49" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="49" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B49" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C49" s="36">
+      <c r="C49" s="32">
         <v>116</v>
       </c>
-      <c r="D49" s="38" t="s">
+      <c r="D49" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="E49" s="38" t="s">
+      <c r="E49" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="F49" s="39" t="s">
+      <c r="F49" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="G49" s="40" t="s">
+      <c r="G49" s="35"/>
+      <c r="H49" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="H49" s="44" t="s">
+      <c r="I49" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="I49" s="42" t="s">
+      <c r="J49" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="J49" s="43" t="s">
+      <c r="K49" s="39" t="s">
         <v>193</v>
       </c>
-      <c r="K49" s="44" t="s">
+      <c r="L49" s="35" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="50" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B50" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C50" s="36">
+      <c r="C50" s="32">
         <v>118</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="22" t="s">
         <v>340</v>
       </c>
-      <c r="E50" s="38" t="s">
+      <c r="E50" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="F50" s="39" t="s">
+      <c r="F50" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="G50" s="40" t="s">
+      <c r="G50" s="35" t="s">
+        <v>349</v>
+      </c>
+      <c r="H50" s="36" t="s">
         <v>341</v>
       </c>
-      <c r="H50" s="41">
+      <c r="I50" s="37">
         <v>253535425</v>
       </c>
-      <c r="I50" s="42" t="s">
+      <c r="J50" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="J50" s="43" t="s">
+      <c r="K50" s="39" t="s">
         <v>280</v>
       </c>
-      <c r="K50" s="44" t="s">
+      <c r="L50" s="35" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="2:11" ht="21" customHeight="1">
+    <row r="51" spans="2:12" ht="21" customHeight="1">
       <c r="B51" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="21">
         <v>120</v>
       </c>
-      <c r="D51" s="23" t="s">
+      <c r="D51" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="E51" s="24" t="s">
+      <c r="E51" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="F51" s="25" t="s">
+      <c r="F51" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="G51" s="26" t="s">
+      <c r="G51" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="H51" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="H51" s="27">
+      <c r="I51" s="26">
         <v>289572050</v>
       </c>
-      <c r="I51" s="28" t="s">
+      <c r="J51" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="J51" s="43" t="s">
+      <c r="K51" s="39" t="s">
         <v>335</v>
       </c>
-      <c r="K51" s="31" t="s">
+      <c r="L51" s="24" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="52" spans="2:11" ht="21" customHeight="1">
+    <row r="52" spans="2:12" ht="21" customHeight="1">
       <c r="B52" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="21">
         <v>121</v>
       </c>
-      <c r="D52" s="23" t="s">
+      <c r="D52" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="E52" s="24" t="s">
+      <c r="E52" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="F52" s="25" t="s">
+      <c r="F52" s="24" t="s">
         <v>222</v>
       </c>
-      <c r="G52" s="26" t="s">
+      <c r="G52" s="24"/>
+      <c r="H52" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="H52" s="27">
+      <c r="I52" s="26">
         <v>219947130</v>
       </c>
-      <c r="I52" s="28">
+      <c r="J52" s="27">
         <v>219947138</v>
       </c>
-      <c r="J52" s="29" t="s">
+      <c r="K52" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="K52" s="31" t="s">
+      <c r="L52" s="24" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="53" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="53" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B53" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C53" s="36">
+      <c r="C53" s="32">
         <v>123</v>
       </c>
-      <c r="D53" s="37" t="s">
+      <c r="D53" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="E53" s="38" t="s">
+      <c r="E53" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="F53" s="39" t="s">
+      <c r="F53" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="G53" s="40" t="s">
+      <c r="G53" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="H53" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="H53" s="44" t="s">
+      <c r="I53" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="I53" s="42" t="s">
+      <c r="J53" s="38" t="s">
         <v>276</v>
       </c>
-      <c r="J53" s="43" t="s">
+      <c r="K53" s="39" t="s">
         <v>342</v>
       </c>
-      <c r="K53" s="44" t="s">
+      <c r="L53" s="35" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="54" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="54" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B54" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C54" s="36">
+      <c r="C54" s="32">
         <v>125</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="D54" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="E54" s="38" t="s">
+      <c r="E54" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="F54" s="39" t="s">
+      <c r="F54" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="G54" s="40" t="s">
+      <c r="G54" s="35"/>
+      <c r="H54" s="36" t="s">
         <v>245</v>
       </c>
-      <c r="H54" s="41">
+      <c r="I54" s="37">
         <v>214681766</v>
       </c>
-      <c r="I54" s="42">
+      <c r="J54" s="38">
         <v>214665398</v>
       </c>
-      <c r="J54" s="43" t="s">
+      <c r="K54" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="K54" s="44" t="s">
+      <c r="L54" s="35" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="55" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="55" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B55" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C55" s="47">
+      <c r="C55" s="41">
         <v>126</v>
       </c>
-      <c r="D55" s="37" t="s">
+      <c r="D55" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="E55" s="48" t="s">
+      <c r="E55" s="42" t="s">
         <v>337</v>
       </c>
-      <c r="F55" s="49" t="s">
+      <c r="F55" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="G55" s="50" t="s">
+      <c r="G55" s="43"/>
+      <c r="H55" s="44" t="s">
         <v>255</v>
       </c>
-      <c r="H55" s="41" t="s">
+      <c r="I55" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="I55" s="51"/>
-      <c r="J55" s="52" t="s">
+      <c r="J55" s="45"/>
+      <c r="K55" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="K55" s="53" t="s">
+      <c r="L55" s="43" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="56" spans="2:11" s="12" customFormat="1" ht="38.25" customHeight="1">
+    <row r="56" spans="2:12" s="12" customFormat="1" ht="38.25" customHeight="1">
       <c r="B56" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C56" s="47">
+      <c r="C56" s="41">
         <v>127</v>
       </c>
-      <c r="D56" s="38" t="s">
+      <c r="D56" s="34" t="s">
         <v>308</v>
       </c>
-      <c r="E56" s="48" t="s">
+      <c r="E56" s="42" t="s">
         <v>303</v>
       </c>
-      <c r="F56" s="49" t="s">
+      <c r="F56" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="G56" s="50" t="s">
+      <c r="G56" s="43" t="s">
+        <v>349</v>
+      </c>
+      <c r="H56" s="44" t="s">
         <v>284</v>
       </c>
-      <c r="H56" s="54" t="s">
+      <c r="I56" s="47" t="s">
         <v>307</v>
       </c>
-      <c r="I56" s="51">
+      <c r="J56" s="45">
         <v>253691404</v>
       </c>
-      <c r="J56" s="55" t="s">
+      <c r="K56" s="48" t="s">
         <v>306</v>
       </c>
-      <c r="K56" s="53" t="s">
+      <c r="L56" s="43" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="57" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1" thickBot="1">
+    <row r="57" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="B57" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C57" s="56">
+      <c r="C57" s="49">
         <v>128</v>
       </c>
-      <c r="D57" s="57" t="s">
+      <c r="D57" s="50" t="s">
         <v>297</v>
       </c>
-      <c r="E57" s="58" t="s">
+      <c r="E57" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F57" s="59" t="s">
+      <c r="F57" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="G57" s="60" t="s">
+      <c r="G57" s="52" t="s">
+        <v>346</v>
+      </c>
+      <c r="H57" s="53" t="s">
         <v>298</v>
       </c>
-      <c r="H57" s="61" t="s">
+      <c r="I57" s="54" t="s">
         <v>305</v>
       </c>
-      <c r="I57" s="62"/>
-      <c r="J57" s="63" t="s">
+      <c r="J57" s="55"/>
+      <c r="K57" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="K57" s="64" t="s">
+      <c r="L57" s="52" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="58" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1">
+    <row r="58" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1">
       <c r="B58" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C58" s="65">
+      <c r="C58" s="57">
         <v>501</v>
       </c>
-      <c r="D58" s="66" t="s">
+      <c r="D58" s="58" t="s">
         <v>258</v>
       </c>
-      <c r="E58" s="67" t="s">
+      <c r="E58" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="F58" s="68" t="s">
+      <c r="F58" s="60" t="s">
         <v>264</v>
       </c>
-      <c r="G58" s="69" t="s">
+      <c r="G58" s="60" t="s">
+        <v>352</v>
+      </c>
+      <c r="H58" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="H58" s="70">
+      <c r="I58" s="62">
         <v>229608317</v>
       </c>
-      <c r="I58" s="71">
+      <c r="J58" s="61">
         <v>229601960</v>
       </c>
-      <c r="J58" s="72" t="s">
+      <c r="K58" s="63" t="s">
         <v>259</v>
       </c>
-      <c r="K58" s="73" t="s">
+      <c r="L58" s="60" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="59" spans="2:11" s="12" customFormat="1" ht="21" customHeight="1" thickBot="1">
+    <row r="59" spans="2:12" s="12" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="B59" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C59" s="56">
+      <c r="C59" s="49">
         <v>502</v>
       </c>
-      <c r="D59" s="57" t="s">
+      <c r="D59" s="50" t="s">
         <v>266</v>
       </c>
-      <c r="E59" s="74" t="s">
+      <c r="E59" s="64" t="s">
         <v>296</v>
       </c>
-      <c r="F59" s="75" t="s">
+      <c r="F59" s="65" t="s">
         <v>267</v>
       </c>
-      <c r="G59" s="76" t="s">
+      <c r="G59" s="65" t="s">
+        <v>349</v>
+      </c>
+      <c r="H59" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="H59" s="77">
+      <c r="I59" s="67">
         <v>252311455</v>
       </c>
-      <c r="I59" s="78">
+      <c r="J59" s="68">
         <v>252311401</v>
       </c>
-      <c r="J59" s="79" t="s">
+      <c r="K59" s="69" t="s">
         <v>281</v>
       </c>
-      <c r="K59" s="80" t="s">
+      <c r="L59" s="65" t="s">
         <v>268</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J4" r:id="rId1" xr:uid="{AF4ABF63-2487-4F54-AB7D-DF5ACB8A0CA4}"/>
-    <hyperlink ref="J18" r:id="rId2" xr:uid="{84519CF3-7021-472E-A5B2-BE56E07DCCB9}"/>
-    <hyperlink ref="J8" r:id="rId3" xr:uid="{7AEC8E4F-D58E-4B1C-A437-D9AF6678BA06}"/>
-    <hyperlink ref="J26" r:id="rId4" display="mailto:almerindo.santos@sapo.pt" xr:uid="{B44FE34C-4753-4D42-9180-1B9BE3B4BDEA}"/>
-    <hyperlink ref="J25" r:id="rId5" xr:uid="{F1733FF2-E0FD-47FF-A288-5575908A3C50}"/>
-    <hyperlink ref="J31" r:id="rId6" xr:uid="{448E0AF6-C95B-4868-9F4A-980FFFDE2DF9}"/>
-    <hyperlink ref="J49" r:id="rId7" xr:uid="{9EC60F48-4175-48DE-94B4-53891E346105}"/>
-    <hyperlink ref="J48" r:id="rId8" xr:uid="{74D79119-F241-401D-A6FA-674C89E80D48}"/>
-    <hyperlink ref="J6" r:id="rId9" xr:uid="{E963464F-8CEE-4AFA-93E8-7FB14661167E}"/>
-    <hyperlink ref="J12" r:id="rId10" xr:uid="{E612ED9D-BEB9-4F04-BFE6-3A2090350E52}"/>
-    <hyperlink ref="J10" r:id="rId11" xr:uid="{263566A3-D961-4A2A-9D5E-AA85F4DD1B64}"/>
-    <hyperlink ref="J56" r:id="rId12" display="geral@conficar.pt" xr:uid="{B500CD7D-0267-4C41-9CB8-7BAE86FA8A4A}"/>
-    <hyperlink ref="J30" r:id="rId13" xr:uid="{8265223E-2905-4B97-819A-EDACB9E70582}"/>
-    <hyperlink ref="J58" r:id="rId14" xr:uid="{5EF8C499-B079-4F5F-9225-D54EA019608B}"/>
-    <hyperlink ref="J59" r:id="rId15" xr:uid="{2FC247AA-BD67-4942-9C14-0E0FCC51F32E}"/>
-    <hyperlink ref="J15" r:id="rId16" xr:uid="{98840174-846A-4D65-994F-67D9FFF860BD}"/>
-    <hyperlink ref="J21" r:id="rId17" xr:uid="{68D2D6AE-7FF0-4DD3-838A-2F1E6EA713A7}"/>
-    <hyperlink ref="J11" r:id="rId18" display="mailto:pneus.poco.bispo@gmail.com" xr:uid="{384A51F0-A737-443D-BF18-33A796761EC3}"/>
-    <hyperlink ref="J36" r:id="rId19" xr:uid="{16C74ECF-5E2A-4E67-88F4-8E84ECEEB50A}"/>
-    <hyperlink ref="J37:J47" r:id="rId20" display="geral@jalves.pt " xr:uid="{F9E3F998-61DA-4D26-B214-E0D83D2AE35C}"/>
-    <hyperlink ref="J51" r:id="rId21" display="mailto:geral@autocferreiras.com" xr:uid="{45B0F7CA-04DA-4670-A642-A5C991C7E3B4}"/>
+    <hyperlink ref="K4" r:id="rId1" xr:uid="{AF4ABF63-2487-4F54-AB7D-DF5ACB8A0CA4}"/>
+    <hyperlink ref="K18" r:id="rId2" xr:uid="{84519CF3-7021-472E-A5B2-BE56E07DCCB9}"/>
+    <hyperlink ref="K8" r:id="rId3" xr:uid="{7AEC8E4F-D58E-4B1C-A437-D9AF6678BA06}"/>
+    <hyperlink ref="K26" r:id="rId4" display="mailto:almerindo.santos@sapo.pt" xr:uid="{B44FE34C-4753-4D42-9180-1B9BE3B4BDEA}"/>
+    <hyperlink ref="K25" r:id="rId5" xr:uid="{F1733FF2-E0FD-47FF-A288-5575908A3C50}"/>
+    <hyperlink ref="K31" r:id="rId6" xr:uid="{448E0AF6-C95B-4868-9F4A-980FFFDE2DF9}"/>
+    <hyperlink ref="K49" r:id="rId7" xr:uid="{9EC60F48-4175-48DE-94B4-53891E346105}"/>
+    <hyperlink ref="K48" r:id="rId8" xr:uid="{74D79119-F241-401D-A6FA-674C89E80D48}"/>
+    <hyperlink ref="K6" r:id="rId9" xr:uid="{E963464F-8CEE-4AFA-93E8-7FB14661167E}"/>
+    <hyperlink ref="K12" r:id="rId10" xr:uid="{E612ED9D-BEB9-4F04-BFE6-3A2090350E52}"/>
+    <hyperlink ref="K10" r:id="rId11" xr:uid="{263566A3-D961-4A2A-9D5E-AA85F4DD1B64}"/>
+    <hyperlink ref="K56" r:id="rId12" display="geral@conficar.pt" xr:uid="{B500CD7D-0267-4C41-9CB8-7BAE86FA8A4A}"/>
+    <hyperlink ref="K30" r:id="rId13" xr:uid="{8265223E-2905-4B97-819A-EDACB9E70582}"/>
+    <hyperlink ref="K58" r:id="rId14" xr:uid="{5EF8C499-B079-4F5F-9225-D54EA019608B}"/>
+    <hyperlink ref="K59" r:id="rId15" xr:uid="{2FC247AA-BD67-4942-9C14-0E0FCC51F32E}"/>
+    <hyperlink ref="K15" r:id="rId16" xr:uid="{98840174-846A-4D65-994F-67D9FFF860BD}"/>
+    <hyperlink ref="K21" r:id="rId17" xr:uid="{68D2D6AE-7FF0-4DD3-838A-2F1E6EA713A7}"/>
+    <hyperlink ref="K11" r:id="rId18" display="mailto:pneus.poco.bispo@gmail.com" xr:uid="{384A51F0-A737-443D-BF18-33A796761EC3}"/>
+    <hyperlink ref="K36" r:id="rId19" xr:uid="{16C74ECF-5E2A-4E67-88F4-8E84ECEEB50A}"/>
+    <hyperlink ref="K37:K47" r:id="rId20" display="geral@jalves.pt " xr:uid="{F9E3F998-61DA-4D26-B214-E0D83D2AE35C}"/>
+    <hyperlink ref="K51" r:id="rId21" display="mailto:geral@autocferreiras.com" xr:uid="{45B0F7CA-04DA-4670-A642-A5C991C7E3B4}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
@@ -4218,7 +4311,7 @@
     <oddFooter>Página &amp;P</oddFooter>
   </headerFooter>
   <ignoredErrors>
-    <ignoredError sqref="I6:I20 I56:I59 I48:I54 I40:I42 I43:I46 I21:I25 I26:I38" numberStoredAsText="1"/>
+    <ignoredError sqref="J6:J20 J56:J59 J48:J54 J40:J42 J43:J46 J21:J25 J26:J38" numberStoredAsText="1"/>
   </ignoredErrors>
   <drawing r:id="rId23"/>
 </worksheet>
